--- a/data/input/department_tracking.xlsx
+++ b/data/input/department_tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ADriscoll/Documents/GitHub/implied_data/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC0C1890-072D-1740-A361-C8582F664B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0B019B-FC55-8D41-BA28-8C49B6512865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17060" xr2:uid="{484B642E-F565-954E-B324-BC6070DF60AE}"/>
+    <workbookView xWindow="12880" yWindow="760" windowWidth="14340" windowHeight="17060" xr2:uid="{484B642E-F565-954E-B324-BC6070DF60AE}"/>
   </bookViews>
   <sheets>
     <sheet name="letters" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="254">
   <si>
     <t>type</t>
   </si>
@@ -790,6 +790,18 @@
   </si>
   <si>
     <t>City Commission on</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>NEEDS</t>
+  </si>
+  <si>
+    <t>done</t>
   </si>
 </sst>
 </file>
@@ -855,17 +867,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1236,17 +1238,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03E8848C-B962-5745-8655-3C2761762076}">
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="7" max="10" width="8.1640625" customWidth="1"/>
+    <col min="10" max="13" width="8.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1263,25 +1265,34 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -1297,11 +1308,11 @@
       <c r="E2" t="s">
         <v>80</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -1317,11 +1328,8 @@
       <c r="E3" t="s">
         <v>82</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>225</v>
       </c>
@@ -1337,11 +1345,8 @@
       <c r="E4" t="s">
         <v>80</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -1357,11 +1362,8 @@
       <c r="E5" t="s">
         <v>82</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>79</v>
       </c>
@@ -1378,10 +1380,19 @@
         <v>82</v>
       </c>
       <c r="F6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>250</v>
+      </c>
+      <c r="I6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1397,14 +1408,20 @@
       <c r="E7" t="s">
         <v>85</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="F7" t="s">
+        <v>250</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="N7" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>236</v>
       </c>
@@ -1420,14 +1437,11 @@
       <c r="E8" t="s">
         <v>80</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="N8" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>78</v>
       </c>
@@ -1443,11 +1457,8 @@
       <c r="E9" t="s">
         <v>82</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>52</v>
       </c>
@@ -1463,11 +1474,8 @@
       <c r="E10" t="s">
         <v>80</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>244</v>
       </c>
@@ -1480,11 +1488,8 @@
       <c r="D11">
         <v>4</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>247</v>
       </c>
@@ -1500,11 +1505,8 @@
       <c r="E12" t="s">
         <v>81</v>
       </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>56</v>
       </c>
@@ -1520,11 +1522,8 @@
       <c r="E13" t="s">
         <v>81</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>243</v>
       </c>
@@ -1540,11 +1539,10 @@
       <c r="E14" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>242</v>
       </c>
@@ -1560,11 +1558,8 @@
       <c r="E15" t="s">
         <v>81</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>248</v>
       </c>
@@ -1580,14 +1575,11 @@
       <c r="E16" t="s">
         <v>84</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="K16" t="s">
+      <c r="N16" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -1603,11 +1595,8 @@
       <c r="E17" t="s">
         <v>80</v>
       </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>241</v>
       </c>
@@ -1623,11 +1612,10 @@
       <c r="E18" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
@@ -1643,11 +1631,11 @@
       <c r="E19" t="s">
         <v>80</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>0.33</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -1663,11 +1651,11 @@
       <c r="E20" t="s">
         <v>80</v>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>0.33</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -1683,17 +1671,17 @@
       <c r="E21" t="s">
         <v>82</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>0.66</v>
       </c>
-      <c r="K21" t="s">
+      <c r="N21" t="s">
         <v>233</v>
       </c>
-      <c r="L21" t="s">
+      <c r="O21" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -1709,14 +1697,14 @@
       <c r="E22" t="s">
         <v>82</v>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>0.66</v>
       </c>
-      <c r="K22" t="s">
+      <c r="N22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>65</v>
       </c>
@@ -1732,14 +1720,14 @@
       <c r="E23" t="s">
         <v>82</v>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>0.66</v>
       </c>
-      <c r="K23" t="s">
+      <c r="N23" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>76</v>
       </c>
@@ -1755,14 +1743,14 @@
       <c r="E24" t="s">
         <v>82</v>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>0.66</v>
       </c>
-      <c r="K24" t="s">
+      <c r="N24" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -1778,11 +1766,11 @@
       <c r="E25" t="s">
         <v>82</v>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>0.66</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>47</v>
       </c>
@@ -1801,29 +1789,35 @@
       <c r="F26">
         <v>1</v>
       </c>
-      <c r="G26" s="3">
-        <v>46156</v>
-      </c>
-      <c r="H26" s="3">
-        <v>46156</v>
-      </c>
-      <c r="I26" s="3">
-        <v>46156</v>
-      </c>
-      <c r="J26" s="3">
-        <v>46156</v>
-      </c>
-      <c r="K26" t="s">
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="N26" t="s">
         <v>231</v>
       </c>
-      <c r="L26" t="s">
+      <c r="O26" t="s">
         <v>232</v>
       </c>
-      <c r="M26" t="s">
+      <c r="P26" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>72</v>
       </c>
@@ -1842,15 +1836,21 @@
       <c r="F27">
         <v>1</v>
       </c>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
       <c r="J27" s="3"/>
-      <c r="K27" t="s">
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>71</v>
       </c>
@@ -1869,20 +1869,26 @@
       <c r="F28">
         <v>1</v>
       </c>
-      <c r="G28" s="3">
-        <v>46161</v>
-      </c>
-      <c r="H28" s="3">
-        <v>46161</v>
-      </c>
-      <c r="I28" s="3">
-        <v>46161</v>
-      </c>
-      <c r="J28" s="3">
-        <v>46161</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -1901,14 +1907,20 @@
       <c r="F29">
         <v>1</v>
       </c>
-      <c r="G29" s="3">
-        <v>46161</v>
-      </c>
-      <c r="H29" s="3">
-        <v>46161</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>89</v>
       </c>
@@ -1927,14 +1939,20 @@
       <c r="F30">
         <v>1</v>
       </c>
-      <c r="G30" s="3">
-        <v>46161</v>
-      </c>
-      <c r="H30" s="3">
-        <v>46161</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>75</v>
       </c>
@@ -1953,14 +1971,20 @@
       <c r="F31">
         <v>1</v>
       </c>
-      <c r="G31" s="3">
-        <v>46161</v>
-      </c>
-      <c r="H31" s="3">
-        <v>46161</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>64</v>
       </c>
@@ -1979,17 +2003,23 @@
       <c r="F32">
         <v>1</v>
       </c>
-      <c r="G32" s="3">
-        <v>46161</v>
-      </c>
-      <c r="H32" s="3">
-        <v>46161</v>
-      </c>
-      <c r="K32" t="s">
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="N32" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -2008,14 +2038,20 @@
       <c r="F33">
         <v>1</v>
       </c>
-      <c r="G33" s="3">
-        <v>46162</v>
-      </c>
-      <c r="H33" s="3">
-        <v>46162</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>21</v>
       </c>
@@ -2034,20 +2070,26 @@
       <c r="F34">
         <v>1</v>
       </c>
-      <c r="G34" s="3">
-        <v>46163</v>
-      </c>
-      <c r="H34" s="3">
-        <v>46163</v>
-      </c>
-      <c r="I34" s="3">
-        <v>46163</v>
-      </c>
-      <c r="J34" s="3">
-        <v>46163</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>77</v>
       </c>
@@ -2066,17 +2108,23 @@
       <c r="F35">
         <v>1</v>
       </c>
-      <c r="G35" s="3">
-        <v>46163</v>
-      </c>
-      <c r="H35" s="3">
-        <v>46163</v>
-      </c>
-      <c r="K35" t="s">
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="N35" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -2095,14 +2143,20 @@
       <c r="F36">
         <v>1</v>
       </c>
-      <c r="K36" t="s">
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="N36" t="s">
         <v>227</v>
       </c>
-      <c r="L36" t="s">
+      <c r="O36" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -2121,11 +2175,17 @@
       <c r="F37">
         <v>1</v>
       </c>
-      <c r="K37" t="s">
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="N37" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>29</v>
       </c>
@@ -2144,11 +2204,17 @@
       <c r="F38">
         <v>1</v>
       </c>
-      <c r="K38" t="s">
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="N38" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>62</v>
       </c>
@@ -2167,8 +2233,14 @@
       <c r="F39">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>35</v>
       </c>
@@ -2187,8 +2259,14 @@
       <c r="F40">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>10</v>
       </c>
@@ -2207,8 +2285,14 @@
       <c r="F41">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -2227,34 +2311,35 @@
       <c r="F42">
         <v>1</v>
       </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M42">
-    <sortCondition ref="F1:F42"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P42">
+    <sortCondition ref="I1:I42"/>
   </sortState>
-  <conditionalFormatting sqref="J1 J3:J33 G26:I28 J35:J1048576">
-    <cfRule type="containsBlanks" dxfId="4" priority="7">
-      <formula>LEN(TRIM(G1))=0</formula>
+  <conditionalFormatting sqref="J3:L25 J27:L27 J26:M26 L29:L33 J28:M28 J36:L42 L34:M34 L35 J29:K35">
+    <cfRule type="containsBlanks" dxfId="3" priority="2">
+      <formula>LEN(TRIM(J3))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:J2 G3:I25 I29:I32 G33:I42">
-    <cfRule type="containsBlanks" dxfId="3" priority="4">
-      <formula>LEN(TRIM(G2))=0</formula>
+  <conditionalFormatting sqref="J2:M2">
+    <cfRule type="containsBlanks" dxfId="2" priority="4">
+      <formula>LEN(TRIM(J2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G29:G32">
-    <cfRule type="containsBlanks" dxfId="2" priority="3">
-      <formula>LEN(TRIM(G29))=0</formula>
+  <conditionalFormatting sqref="M1">
+    <cfRule type="containsBlanks" dxfId="1" priority="7">
+      <formula>LEN(TRIM(M1))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H29:H32">
-    <cfRule type="containsBlanks" dxfId="1" priority="2">
-      <formula>LEN(TRIM(H29))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J34">
+  <conditionalFormatting sqref="M3:M25 M27 M29:M33 M35:M1048576">
     <cfRule type="containsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(J34))=0</formula>
+      <formula>LEN(TRIM(M3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
